--- a/output/pdf_financials_xlsx/RGC.xlsx
+++ b/output/pdf_financials_xlsx/RGC.xlsx
@@ -2478,19 +2478,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.003145</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.030627</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.090882</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.917878</v>
       </c>
     </row>
     <row r="93">
@@ -3038,10 +3038,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>0.094273</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.048047</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -3948,7 +3948,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.043</v>
       </c>
@@ -6248,7 +6252,11 @@
           <t>Decommissioning expense, included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RGC.xlsx
+++ b/output/pdf_financials_xlsx/RGC.xlsx
@@ -672,16 +672,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.020201</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006622</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.092502</v>
       </c>
     </row>
     <row r="13">
@@ -1022,16 +1022,16 @@
         <v>-2.543094</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.087945</v>
+        <v>-6.108146</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.40458</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.634596</v>
+        <v>-3.641218</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.427828999999999</v>
+        <v>-8.520331000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1066,16 +1066,16 @@
         <v>-2.543094</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.087945</v>
+        <v>-6.108146</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.40458</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.634596</v>
+        <v>-3.641218</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.427828999999999</v>
+        <v>-8.520331000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.508999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.197916</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.051581</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.197193</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.766805</v>
       </c>
     </row>
     <row r="35">
@@ -1222,19 +1222,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.508999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.197916</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.051581</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.197193</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.766805</v>
       </c>
     </row>
     <row r="37">
@@ -1486,19 +1486,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.889339</v>
+        <v>0.38034</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.268492</v>
+        <v>0.070576</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.10504</v>
+        <v>0.053459</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.286453</v>
+        <v>0.08926000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.028968</v>
+        <v>0.262163</v>
       </c>
     </row>
     <row r="49">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">

--- a/output/pdf_financials_xlsx/RGC.xlsx
+++ b/output/pdf_financials_xlsx/RGC.xlsx
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.15541</v>
       </c>
     </row>
     <row r="112">
@@ -3409,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.15541</v>
       </c>
     </row>
     <row r="135">
@@ -3431,7 +3431,7 @@
         <v>-3.696697</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-7.443984</v>
+        <v>-7.599394</v>
       </c>
     </row>
   </sheetData>
@@ -4921,7 +4921,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
